--- a/resources/节点表头映射关系.xlsx
+++ b/resources/节点表头映射关系.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12345" windowHeight="5145"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>属性</t>
   </si>
@@ -57,6 +57,18 @@
   </si>
   <si>
     <t>根据节点相连道路映射后的道路等级进行判断，但先全部按“信号控制交叉口”输入</t>
+  </si>
+  <si>
+    <t>经度</t>
+  </si>
+  <si>
+    <t>x_coord</t>
+  </si>
+  <si>
+    <t>纬度</t>
+  </si>
+  <si>
+    <t>y_coord</t>
   </si>
   <si>
     <t>矢量数据</t>
@@ -1055,8 +1067,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="20.25" customWidth="1"/>
     <col min="4" max="4" width="21.25" customWidth="1"/>
@@ -1112,10 +1124,38 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
